--- a/pricing/Clean_and_Green_KillAndReseed_Pricing.xlsx
+++ b/pricing/Clean_and_Green_KillAndReseed_Pricing.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Materials Catalog" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phase 1 - Kill" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Phase 2 - Prep" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Phase 3 - Seed" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Phase 4 - Establish" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Project Total" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials Catalog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 - Kill" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 - Prep" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3 - Seed" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 4 - Establish" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Total" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="LawnSize">Assumptions!$B$3</definedName>
@@ -648,7 +648,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clean and Green Lawn Care  |  Lawn Renovation Proposal</t>
+          <t>Clean and Green Turf  |  Lawn Renovation Proposal</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Clean and Green Lawn Care - Authorized Representative</t>
+          <t>Clean and Green Turf, LLC - Authorized Representative</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Assumptions  |  Clean and Green Lawn Care</t>
+          <t>Assumptions  |  Clean and Green Turf  |  Renovation and Lawn Care</t>
         </is>
       </c>
     </row>
